--- a/Training Data/Automation/MS-NID.xlsx
+++ b/Training Data/Automation/MS-NID.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\SMS_Automation\Training Data\Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26510129-E9D6-49BF-9403-A5A1B4A4A4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0D9248-1BD8-40B8-8EE2-131565EC2EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MS-NID" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
-  <si>
-    <t>SL No</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Request</t>
   </si>
@@ -31,152 +28,85 @@
     <t>Reply</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>MS-NID 01612196151</t>
   </si>
   <si>
     <t>MSISDN: 8801612196151, NID: 7305979036, DoB: 02/05/1972 [Robi]</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>MS-NID 09638065277</t>
-  </si>
-  <si>
-    <t>(Reply not visible - possibly searched as 09638065278)</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>MS-NID 09638065278</t>
-  </si>
-  <si>
-    <t>(No reply visible in loaded messages)</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>(Searched again by Inspector Oc Banaripara at 15:19 - no visible reply)</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>MS-NID 01307468725</t>
   </si>
   <si>
     <t>MSISDN: 8801307468725, 0611073766793, 1958-03-12 [GP]</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>MS-NID 01757265392</t>
-  </si>
-  <si>
-    <t>(Split from 5-number batch: MS-NID 01757265392 01844468499 01768233922 01736373112 01757232333)</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>MS-NID 01844468499</t>
-  </si>
-  <si>
-    <t>(Split from 5-number batch - see above)</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>MS-NID 01768233922</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>MS-NID 01736373112</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>MS-NID 01757232333</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>MS-NID 01794702044</t>
   </si>
   <si>
     <t>MSISDN: 8801794702044, 0619452170146, 1970-11-09 [GP]</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>MS-NID 01304277436</t>
   </si>
   <si>
     <t>MSISDN: 8801304277436, 0619442156020, 1985-03-02 [GP]</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>MS-NID 01715679017</t>
   </si>
   <si>
     <t>MSISDN: 8801715679017 - Sorry No records found</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>MS-NID 01743739121</t>
   </si>
   <si>
     <t>MSISDN: 8801743739121, 0619452170225, 1972-12-21 [GP]</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>MS-NID 01761606344</t>
   </si>
   <si>
     <t>MSISDN: 8801761606344, 5552667254, 1997-06-15 [GP]</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>MS-NID 01765769349</t>
-  </si>
-  <si>
-    <t>(Reply not visible for this request from Inspector Oc Gournadi at 22:58)</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>MS-NID 01739204760</t>
   </si>
   <si>
     <t>MSISDN: 8801739204760, 9553747057, 1983-01-01 [GP]</t>
+  </si>
+  <si>
+    <t>MSISDN?8801994428200 NID ?8248705892?
+Date of Birth?1980-01-03</t>
+  </si>
+  <si>
+    <t>MS -NID 8801994428200</t>
+  </si>
+  <si>
+    <t>SL NO</t>
+  </si>
+  <si>
+    <t>MSISDN: 8801842615514
+NID: 6856765273
+DoB: 01/01/1989 [Robi]</t>
+  </si>
+  <si>
+    <t>MS-NID 8801842615514</t>
+  </si>
+  <si>
+    <t>MS-NID 01990169712</t>
+  </si>
+  <si>
+    <t>MSISDN?8801990169712 national_id?
+Document Number?19790619431282189?
+Date of Birth?1979-01-01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,8 +241,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -492,8 +428,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -608,6 +550,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -653,13 +608,25 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -706,7 +673,20 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -717,6 +697,16 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0247DF39-8DB6-46DB-A503-184C0D447B03}" name="Table1" displayName="Table1" ref="B2:C16" headerRowCount="0" totalsRowShown="0">
+  <tableColumns count="2">
+    <tableColumn id="2" xr3:uid="{7D16482E-AEB6-40B8-AF25-B22E6FAE885B}" name="Column2" headerRowDxfId="3" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{B92D272C-C50B-4A58-8D48-62AA928425A5}" name="Column3" headerRowDxfId="1" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1036,213 +1026,170 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="8.83984375" style="1"/>
-    <col min="2" max="2" width="23.3125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="86.83984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" style="1"/>
+    <col min="2" max="2" width="23.31640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="86.81640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="B1"/>
+      <c r="C1"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A3" s="6">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="44.25" x14ac:dyDescent="0.75">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="44.25" x14ac:dyDescent="0.75">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>49</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Training Data/Automation/MS-NID.xlsx
+++ b/Training Data/Automation/MS-NID.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\SMS_Automation\Training Data\Automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\GitHub\SMS_Automation\Training Data\Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0D9248-1BD8-40B8-8EE2-131565EC2EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF0D113B-D08E-4F6C-9254-07A02C1E14B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MS-NID" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Request</t>
   </si>
@@ -100,13 +100,50 @@
     <t>MSISDN?8801990169712 national_id?
 Document Number?19790619431282189?
 Date of Birth?1979-01-01</t>
+  </si>
+  <si>
+    <t>MS-NID 01881986611</t>
+  </si>
+  <si>
+    <t>MSISDN: 8801881986611
+NID: 2854786395
+DoB: 11/03/1996 [Robi]</t>
+  </si>
+  <si>
+    <t>MS-NID 01600204240</t>
+  </si>
+  <si>
+    <t>MS-NID 01603990945</t>
+  </si>
+  <si>
+    <t>MSISDN: 8801603990945
+NID: 3769269055
+DoB: 12/20/2003 [Robi]</t>
+  </si>
+  <si>
+    <t>MSISDN: 8801600204240
+NID: 5561211730
+DoB: 01/07/2001 [Robi]</t>
+  </si>
+  <si>
+    <t>01904809964 NID 19912610457000031  DOB 10.12.1991</t>
+  </si>
+  <si>
+    <t>MS-NID 01603990946</t>
+  </si>
+  <si>
+    <t>MS-NID 01938590648</t>
+  </si>
+  <si>
+    <t>MSISDN?8801938590648 NID 5108405506?
+Date of Birth?2001-01-12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -619,13 +656,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -700,7 +737,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0247DF39-8DB6-46DB-A503-184C0D447B03}" name="Table1" displayName="Table1" ref="B2:C16" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0247DF39-8DB6-46DB-A503-184C0D447B03}" name="Table1" displayName="Table1" ref="B1:C17" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="2" xr3:uid="{7D16482E-AEB6-40B8-AF25-B22E6FAE885B}" name="Column2" headerRowDxfId="3" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{B92D272C-C50B-4A58-8D48-62AA928425A5}" name="Column3" headerRowDxfId="1" dataDxfId="0"/>
@@ -1026,163 +1063,214 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="1"/>
-    <col min="2" max="2" width="23.31640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="86.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" style="1"/>
+    <col min="2" max="2" width="23.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="86.875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="B1"/>
-      <c r="C1"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A2" s="4" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
       <c r="B2" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A3" s="6">
-        <v>1</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4">
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A4" s="4">
-        <v>3</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="5">
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
       <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="5">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="5">
         <v>8</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="28.5">
+      <c r="A10" s="5">
         <v>10</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="42.75">
+      <c r="A11" s="4">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="42.75">
+      <c r="A12" s="5">
         <v>12</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="42.75">
+      <c r="A13" s="4">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A9" s="5">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="42.75">
+      <c r="A14" s="5">
         <v>14</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="42.75">
+      <c r="A15" s="4">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4">
         <v>16</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="B16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="28.5">
+      <c r="A17" s="5">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="B17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4">
         <v>19</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="44.25" x14ac:dyDescent="0.75">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="44.25" x14ac:dyDescent="0.75">
-      <c r="A13" s="5">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A14" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A15" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A16" s="4">
-        <v>15</v>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="5">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Training Data/Automation/MS-NID.xlsx
+++ b/Training Data/Automation/MS-NID.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\GitHub\SMS_Automation\Training Data\Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26510129-E9D6-49BF-9403-A5A1B4A4A4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF0D113B-D08E-4F6C-9254-07A02C1E14B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MS-NID" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
-  <si>
-    <t>SL No</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Request</t>
   </si>
@@ -31,152 +28,122 @@
     <t>Reply</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>MS-NID 01612196151</t>
   </si>
   <si>
     <t>MSISDN: 8801612196151, NID: 7305979036, DoB: 02/05/1972 [Robi]</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>MS-NID 09638065277</t>
-  </si>
-  <si>
-    <t>(Reply not visible - possibly searched as 09638065278)</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>MS-NID 09638065278</t>
-  </si>
-  <si>
-    <t>(No reply visible in loaded messages)</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>(Searched again by Inspector Oc Banaripara at 15:19 - no visible reply)</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>MS-NID 01307468725</t>
   </si>
   <si>
     <t>MSISDN: 8801307468725, 0611073766793, 1958-03-12 [GP]</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>MS-NID 01757265392</t>
-  </si>
-  <si>
-    <t>(Split from 5-number batch: MS-NID 01757265392 01844468499 01768233922 01736373112 01757232333)</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>MS-NID 01844468499</t>
-  </si>
-  <si>
-    <t>(Split from 5-number batch - see above)</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>MS-NID 01768233922</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>MS-NID 01736373112</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>MS-NID 01757232333</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>MS-NID 01794702044</t>
   </si>
   <si>
     <t>MSISDN: 8801794702044, 0619452170146, 1970-11-09 [GP]</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>MS-NID 01304277436</t>
   </si>
   <si>
     <t>MSISDN: 8801304277436, 0619442156020, 1985-03-02 [GP]</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>MS-NID 01715679017</t>
   </si>
   <si>
     <t>MSISDN: 8801715679017 - Sorry No records found</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>MS-NID 01743739121</t>
   </si>
   <si>
     <t>MSISDN: 8801743739121, 0619452170225, 1972-12-21 [GP]</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>MS-NID 01761606344</t>
   </si>
   <si>
     <t>MSISDN: 8801761606344, 5552667254, 1997-06-15 [GP]</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>MS-NID 01765769349</t>
-  </si>
-  <si>
-    <t>(Reply not visible for this request from Inspector Oc Gournadi at 22:58)</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>MS-NID 01739204760</t>
   </si>
   <si>
     <t>MSISDN: 8801739204760, 9553747057, 1983-01-01 [GP]</t>
+  </si>
+  <si>
+    <t>MSISDN?8801994428200 NID ?8248705892?
+Date of Birth?1980-01-03</t>
+  </si>
+  <si>
+    <t>MS -NID 8801994428200</t>
+  </si>
+  <si>
+    <t>SL NO</t>
+  </si>
+  <si>
+    <t>MSISDN: 8801842615514
+NID: 6856765273
+DoB: 01/01/1989 [Robi]</t>
+  </si>
+  <si>
+    <t>MS-NID 8801842615514</t>
+  </si>
+  <si>
+    <t>MS-NID 01990169712</t>
+  </si>
+  <si>
+    <t>MSISDN?8801990169712 national_id?
+Document Number?19790619431282189?
+Date of Birth?1979-01-01</t>
+  </si>
+  <si>
+    <t>MS-NID 01881986611</t>
+  </si>
+  <si>
+    <t>MSISDN: 8801881986611
+NID: 2854786395
+DoB: 11/03/1996 [Robi]</t>
+  </si>
+  <si>
+    <t>MS-NID 01600204240</t>
+  </si>
+  <si>
+    <t>MS-NID 01603990945</t>
+  </si>
+  <si>
+    <t>MSISDN: 8801603990945
+NID: 3769269055
+DoB: 12/20/2003 [Robi]</t>
+  </si>
+  <si>
+    <t>MSISDN: 8801600204240
+NID: 5561211730
+DoB: 01/07/2001 [Robi]</t>
+  </si>
+  <si>
+    <t>01904809964 NID 19912610457000031  DOB 10.12.1991</t>
+  </si>
+  <si>
+    <t>MS-NID 01603990946</t>
+  </si>
+  <si>
+    <t>MS-NID 01938590648</t>
+  </si>
+  <si>
+    <t>MSISDN?8801938590648 NID 5108405506?
+Date of Birth?2001-01-12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,8 +278,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -492,8 +465,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -608,6 +587,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -653,13 +645,25 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -706,7 +710,20 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -717,6 +734,16 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0247DF39-8DB6-46DB-A503-184C0D447B03}" name="Table1" displayName="Table1" ref="B1:C17" headerRowCount="0" totalsRowShown="0">
+  <tableColumns count="2">
+    <tableColumn id="2" xr3:uid="{7D16482E-AEB6-40B8-AF25-B22E6FAE885B}" name="Column2" headerRowDxfId="3" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{B92D272C-C50B-4A58-8D48-62AA928425A5}" name="Column3" headerRowDxfId="1" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1036,213 +1063,221 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.83984375" style="1"/>
-    <col min="2" max="2" width="23.3125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="86.83984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" style="1"/>
+    <col min="2" max="2" width="23.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="86.875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" s="5">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="4">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="5">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="4">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="5">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="28.5">
+      <c r="A10" s="5">
         <v>10</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="42.75">
+      <c r="A11" s="4">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="42.75">
+      <c r="A12" s="5">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="42.75">
+      <c r="A13" s="4">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="42.75">
+      <c r="A14" s="5">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="42.75">
+      <c r="A15" s="4">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
+      <c r="B16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="28.5">
+      <c r="A17" s="5">
         <v>17</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4">
         <v>18</v>
       </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
+    <row r="20" spans="1:3">
+      <c r="A20" s="5">
         <v>20</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>49</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>